--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/procedure-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -751,7 +751,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -779,7 +779,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter|EpisodeOfCare) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -798,7 +798,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -880,7 +880,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -899,7 +899,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -915,7 +915,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-medicationrequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/medicationrequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1065,7 +1065,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1618,7 +1618,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1641,7 +1641,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/detectedissue-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationdispense-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
